--- a/data/trans_orig/IP74A3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP74A3_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto las cuotas de compras aplazadas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de cuotas de compras aplazadas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>89,03%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>473</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>78,74%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>666</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>286</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
